--- a/docs/app/api/files/results-6.xlsx
+++ b/docs/app/api/files/results-6.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-04 09:46 UTC · 31 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 18:35 UTC · 43 ms</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13423545.25</v>
+        <v>13423698.56</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -563,11 +563,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1845603.64</v>
+        <v>2179520.08</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>worse</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>783.38</v>
+        <v>783.3</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -586,11 +586,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-230.29</v>
+        <v>127.18</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>worse</t>
         </is>
       </c>
     </row>
@@ -609,11 +609,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>worse</t>
         </is>
       </c>
     </row>
@@ -632,11 +632,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.1209</v>
+        <v>0</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>flat</t>
         </is>
       </c>
     </row>
@@ -655,11 +655,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1209</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>flat</t>
         </is>
       </c>
     </row>
@@ -678,11 +678,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.3369</v>
+        <v>0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>flat</t>
         </is>
       </c>
     </row>
@@ -701,11 +701,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.3369</v>
+        <v>0</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>flat</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.1477</v>
+        <v>-0.0192</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-34</v>
+        <v>-5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -770,11 +770,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-19</v>
+        <v>0</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>flat</t>
         </is>
       </c>
     </row>
@@ -940,26 +940,26 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Port Province</t>
+          <t>National Capital District</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>168000</v>
       </c>
       <c r="E2" t="n">
-        <v>587.554</v>
+        <v>588.05</v>
       </c>
       <c r="F2" t="n">
-        <v>587.554</v>
+        <v>588.05</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>299803.31</v>
+        <v>300020.89</v>
       </c>
       <c r="I2" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>0.08</v>
       </c>
       <c r="N2" t="n">
-        <v>108.1</v>
+        <v>108</v>
       </c>
       <c r="O2" t="n">
         <v>0.0262</v>
@@ -1024,7 +1024,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>237789.08</v>
+        <v>237762.98</v>
       </c>
       <c r="I3" t="n">
         <v>1.8</v>
@@ -1092,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>108667.28</v>
+        <v>108655.22</v>
       </c>
       <c r="I4" t="n">
         <v>1.78</v>
@@ -1160,7 +1160,7 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>96536.64999999999</v>
+        <v>96525.97</v>
       </c>
       <c r="I5" t="n">
         <v>1.79</v>
@@ -1228,7 +1228,7 @@
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>68307.22</v>
+        <v>68299.71000000001</v>
       </c>
       <c r="I6" t="n">
         <v>1.8</v>
@@ -1296,7 +1296,7 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>92911.22</v>
+        <v>92901.92</v>
       </c>
       <c r="I7" t="n">
         <v>1.98</v>
@@ -1364,7 +1364,7 @@
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>92092.74000000001</v>
+        <v>92084.44</v>
       </c>
       <c r="I8" t="n">
         <v>2.19</v>
@@ -1432,7 +1432,7 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>42689.59</v>
+        <v>42685.84</v>
       </c>
       <c r="I9" t="n">
         <v>2.25</v>
@@ -1500,7 +1500,7 @@
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>80791.34</v>
+        <v>80783.83</v>
       </c>
       <c r="I10" t="n">
         <v>2.13</v>
@@ -1568,7 +1568,7 @@
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>133409.15</v>
+        <v>133406.78</v>
       </c>
       <c r="I11" t="n">
         <v>11.12</v>
@@ -1636,7 +1636,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>33402.6</v>
+        <v>33399.43</v>
       </c>
       <c r="I12" t="n">
         <v>2.09</v>
@@ -1704,7 +1704,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>139194.3</v>
+        <v>139182.84</v>
       </c>
       <c r="I13" t="n">
         <v>2.4</v>
@@ -1772,7 +1772,7 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>47769.09</v>
+        <v>47764.94</v>
       </c>
       <c r="I14" t="n">
         <v>2.27</v>
@@ -1840,7 +1840,7 @@
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>72791</v>
+        <v>72784.67</v>
       </c>
       <c r="I15" t="n">
         <v>2.27</v>
@@ -1908,7 +1908,7 @@
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>40944.94</v>
+        <v>40941.38</v>
       </c>
       <c r="I16" t="n">
         <v>2.27</v>
@@ -1976,7 +1976,7 @@
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>58377.07</v>
+        <v>58372.33</v>
       </c>
       <c r="I17" t="n">
         <v>2.43</v>
@@ -2044,7 +2044,7 @@
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>128885.41</v>
+        <v>128883.23</v>
       </c>
       <c r="I18" t="n">
         <v>11.72</v>
@@ -2112,7 +2112,7 @@
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>103407.73</v>
+        <v>103399.03</v>
       </c>
       <c r="I19" t="n">
         <v>2.35</v>
@@ -2180,7 +2180,7 @@
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>89455.82000000001</v>
+        <v>89448.11</v>
       </c>
       <c r="I20" t="n">
         <v>2.29</v>
@@ -2248,7 +2248,7 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>64224.69</v>
+        <v>64219.16</v>
       </c>
       <c r="I21" t="n">
         <v>2.29</v>
@@ -2316,7 +2316,7 @@
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>71105.91</v>
+        <v>71099.78</v>
       </c>
       <c r="I22" t="n">
         <v>2.29</v>
@@ -2384,7 +2384,7 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>101802.64</v>
+        <v>101800.86</v>
       </c>
       <c r="I23" t="n">
         <v>11.31</v>
@@ -2452,7 +2452,7 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>96146.92999999999</v>
+        <v>96145.25</v>
       </c>
       <c r="I24" t="n">
         <v>11.31</v>
@@ -2520,7 +2520,7 @@
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>17203.04</v>
+        <v>17201.56</v>
       </c>
       <c r="I25" t="n">
         <v>2.29</v>
@@ -2588,7 +2588,7 @@
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>139043.83</v>
+        <v>139031.57</v>
       </c>
       <c r="I26" t="n">
         <v>2.24</v>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Losuia Province</t>
+          <t>Milne Bay</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -2656,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>96233.34</v>
+        <v>96227.61</v>
       </c>
       <c r="I27" t="n">
         <v>3.32</v>
@@ -2724,7 +2724,7 @@
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>65589.39</v>
+        <v>65585.24000000001</v>
       </c>
       <c r="I28" t="n">
         <v>3.12</v>
@@ -2792,7 +2792,7 @@
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>69685.59</v>
+        <v>69680.84</v>
       </c>
       <c r="I29" t="n">
         <v>2.9</v>
@@ -2860,7 +2860,7 @@
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>40649.93</v>
+        <v>40647.16</v>
       </c>
       <c r="I30" t="n">
         <v>2.9</v>
@@ -2928,7 +2928,7 @@
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>38124.92</v>
+        <v>38121.56</v>
       </c>
       <c r="I31" t="n">
         <v>2.24</v>
@@ -2996,7 +2996,7 @@
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>45309.77</v>
+        <v>45306.81</v>
       </c>
       <c r="I32" t="n">
         <v>3.02</v>
@@ -3064,7 +3064,7 @@
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>173563.69</v>
+        <v>173549.66</v>
       </c>
       <c r="I33" t="n">
         <v>2.44</v>
@@ -3132,7 +3132,7 @@
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>53780.3</v>
+        <v>53775.95</v>
       </c>
       <c r="I34" t="n">
         <v>2.44</v>
@@ -3200,7 +3200,7 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>31779.27</v>
+        <v>31776.7</v>
       </c>
       <c r="I35" t="n">
         <v>2.44</v>
@@ -3268,7 +3268,7 @@
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>114966.3</v>
+        <v>114964.32</v>
       </c>
       <c r="I36" t="n">
         <v>11.5</v>
@@ -3336,7 +3336,7 @@
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>26890.15</v>
+        <v>26887.97</v>
       </c>
       <c r="I37" t="n">
         <v>2.44</v>
@@ -3404,7 +3404,7 @@
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>34223.83</v>
+        <v>34221.06</v>
       </c>
       <c r="I38" t="n">
         <v>2.44</v>
@@ -3456,26 +3456,26 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Angau Province</t>
+          <t>Morobe</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>188000</v>
       </c>
       <c r="E39" t="n">
-        <v>656.3200000000001</v>
+        <v>658.056</v>
       </c>
       <c r="F39" t="n">
-        <v>656.3200000000001</v>
+        <v>658.056</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>367529.97</v>
+        <v>368456.92</v>
       </c>
       <c r="I39" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>0.08</v>
       </c>
       <c r="N39" t="n">
-        <v>108.3</v>
+        <v>108</v>
       </c>
       <c r="O39" t="n">
         <v>0.0252</v>
@@ -3540,7 +3540,7 @@
         <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>116688.59</v>
+        <v>116677.91</v>
       </c>
       <c r="I40" t="n">
         <v>2.16</v>
@@ -3608,7 +3608,7 @@
         <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>69464.39</v>
+        <v>69458.25999999999</v>
       </c>
       <c r="I41" t="n">
         <v>2.24</v>
@@ -3676,7 +3676,7 @@
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>100556.94</v>
+        <v>100548.63</v>
       </c>
       <c r="I42" t="n">
         <v>2.39</v>
@@ -3744,7 +3744,7 @@
         <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>86645.61</v>
+        <v>86638.49000000001</v>
       </c>
       <c r="I43" t="n">
         <v>2.41</v>
@@ -3812,7 +3812,7 @@
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>210843.24</v>
+        <v>210839.48</v>
       </c>
       <c r="I44" t="n">
         <v>11.1</v>
@@ -3880,7 +3880,7 @@
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>40701.62</v>
+        <v>40698.26</v>
       </c>
       <c r="I45" t="n">
         <v>2.39</v>
@@ -3948,7 +3948,7 @@
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>49216.25</v>
+        <v>49211.7</v>
       </c>
       <c r="I46" t="n">
         <v>2.14</v>
@@ -4000,7 +4000,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Modilon Province</t>
+          <t>Madang</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -4016,7 +4016,7 @@
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>198814.29</v>
+        <v>198795.31</v>
       </c>
       <c r="I47" t="n">
         <v>2.07</v>
@@ -4084,7 +4084,7 @@
         <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>104697.14</v>
+        <v>104689.04</v>
       </c>
       <c r="I48" t="n">
         <v>2.55</v>
@@ -4152,7 +4152,7 @@
         <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>70749.63</v>
+        <v>70744.49000000001</v>
       </c>
       <c r="I49" t="n">
         <v>2.72</v>
@@ -4220,7 +4220,7 @@
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>57641.69</v>
+        <v>57637.34</v>
       </c>
       <c r="I50" t="n">
         <v>2.62</v>
@@ -4288,7 +4288,7 @@
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>66990.67999999999</v>
+        <v>66985.14</v>
       </c>
       <c r="I51" t="n">
         <v>2.39</v>
@@ -4356,7 +4356,7 @@
         <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>130533.11</v>
+        <v>130530.74</v>
       </c>
       <c r="I52" t="n">
         <v>10.88</v>
@@ -4424,7 +4424,7 @@
         <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>165295.16</v>
+        <v>165292.4</v>
       </c>
       <c r="I53" t="n">
         <v>11.81</v>
@@ -4492,7 +4492,7 @@
         <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>220060.94</v>
+        <v>220043.37</v>
       </c>
       <c r="I54" t="n">
         <v>2.5</v>
@@ -4560,7 +4560,7 @@
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>130036.01</v>
+        <v>130025.63</v>
       </c>
       <c r="I55" t="n">
         <v>2.5</v>
@@ -4628,7 +4628,7 @@
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>111649.23</v>
+        <v>111640.44</v>
       </c>
       <c r="I56" t="n">
         <v>2.54</v>
@@ -4696,10 +4696,10 @@
         <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>67084.75</v>
+        <v>67079.96000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>82522.85000000001</v>
+        <v>82516.25999999999</v>
       </c>
       <c r="I58" t="n">
         <v>2.5</v>
@@ -4832,7 +4832,7 @@
         <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v>67518.7</v>
+        <v>67513.31</v>
       </c>
       <c r="I59" t="n">
         <v>2.5</v>
@@ -4900,7 +4900,7 @@
         <v>1</v>
       </c>
       <c r="H60" t="n">
-        <v>40870</v>
+        <v>40867.01</v>
       </c>
       <c r="I60" t="n">
         <v>2.72</v>
@@ -4968,7 +4968,7 @@
         <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>122116.08</v>
+        <v>122106.79</v>
       </c>
       <c r="I61" t="n">
         <v>2.6</v>
@@ -5036,7 +5036,7 @@
         <v>1</v>
       </c>
       <c r="H62" t="n">
-        <v>98599.03999999999</v>
+        <v>98591.25999999999</v>
       </c>
       <c r="I62" t="n">
         <v>2.53</v>
@@ -5104,7 +5104,7 @@
         <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>61307.02</v>
+        <v>61302.23</v>
       </c>
       <c r="I63" t="n">
         <v>2.55</v>
@@ -5172,7 +5172,7 @@
         <v>1</v>
       </c>
       <c r="H64" t="n">
-        <v>55452.96</v>
+        <v>55448.57</v>
       </c>
       <c r="I64" t="n">
         <v>2.52</v>
@@ -5240,7 +5240,7 @@
         <v>1</v>
       </c>
       <c r="H65" t="n">
-        <v>171402.07</v>
+        <v>171398.47</v>
       </c>
       <c r="I65" t="n">
         <v>9.52</v>
@@ -5308,7 +5308,7 @@
         <v>1</v>
       </c>
       <c r="H66" t="n">
-        <v>100653.58</v>
+        <v>100650.98</v>
       </c>
       <c r="I66" t="n">
         <v>7.74</v>
@@ -5376,7 +5376,7 @@
         <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>105727.29</v>
+        <v>105725.09</v>
       </c>
       <c r="I67" t="n">
         <v>9.609999999999999</v>
@@ -5444,7 +5444,7 @@
         <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>165795.44</v>
+        <v>165781.06</v>
       </c>
       <c r="I68" t="n">
         <v>2.3</v>
@@ -5512,7 +5512,7 @@
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>107004.84</v>
+        <v>106995.25</v>
       </c>
       <c r="I69" t="n">
         <v>2.23</v>
@@ -5580,7 +5580,7 @@
         <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>92815.03999999999</v>
+        <v>92807.45</v>
       </c>
       <c r="I70" t="n">
         <v>2.44</v>
@@ -5648,7 +5648,7 @@
         <v>1</v>
       </c>
       <c r="H71" t="n">
-        <v>105309.7</v>
+        <v>105301.52</v>
       </c>
       <c r="I71" t="n">
         <v>2.57</v>
@@ -5716,7 +5716,7 @@
         <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>67730.39</v>
+        <v>67724.60000000001</v>
       </c>
       <c r="I72" t="n">
         <v>2.34</v>
@@ -5784,7 +5784,7 @@
         <v>1</v>
       </c>
       <c r="H73" t="n">
-        <v>76416.25</v>
+        <v>76409.86</v>
       </c>
       <c r="I73" t="n">
         <v>2.39</v>
@@ -5852,7 +5852,7 @@
         <v>1</v>
       </c>
       <c r="H74" t="n">
-        <v>219738.58</v>
+        <v>219721.8</v>
       </c>
       <c r="I74" t="n">
         <v>2.62</v>
@@ -5920,7 +5920,7 @@
         <v>1</v>
       </c>
       <c r="H75" t="n">
-        <v>116397.71</v>
+        <v>116389.13</v>
       </c>
       <c r="I75" t="n">
         <v>2.71</v>
@@ -5988,7 +5988,7 @@
         <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>82489.5</v>
+        <v>82483.31</v>
       </c>
       <c r="I76" t="n">
         <v>2.66</v>
@@ -6056,7 +6056,7 @@
         <v>1</v>
       </c>
       <c r="H77" t="n">
-        <v>68006.36</v>
+        <v>68000.97</v>
       </c>
       <c r="I77" t="n">
         <v>2.52</v>
@@ -6124,7 +6124,7 @@
         <v>1</v>
       </c>
       <c r="H78" t="n">
-        <v>198741.89</v>
+        <v>198738.7</v>
       </c>
       <c r="I78" t="n">
         <v>12.42</v>
@@ -6192,7 +6192,7 @@
         <v>1</v>
       </c>
       <c r="H79" t="n">
-        <v>182489.95</v>
+        <v>182474.17</v>
       </c>
       <c r="I79" t="n">
         <v>2.31</v>
@@ -6260,7 +6260,7 @@
         <v>1</v>
       </c>
       <c r="H80" t="n">
-        <v>99399.33</v>
+        <v>99390.53999999999</v>
       </c>
       <c r="I80" t="n">
         <v>2.26</v>
@@ -6328,7 +6328,7 @@
         <v>1</v>
       </c>
       <c r="H81" t="n">
-        <v>85089.91</v>
+        <v>85082.72</v>
       </c>
       <c r="I81" t="n">
         <v>2.36</v>
@@ -6396,7 +6396,7 @@
         <v>1</v>
       </c>
       <c r="H82" t="n">
-        <v>95384.8</v>
+        <v>95377.00999999999</v>
       </c>
       <c r="I82" t="n">
         <v>2.45</v>
@@ -6464,7 +6464,7 @@
         <v>1</v>
       </c>
       <c r="H83" t="n">
-        <v>55881.64</v>
+        <v>55877.04</v>
       </c>
       <c r="I83" t="n">
         <v>2.43</v>
@@ -6532,7 +6532,7 @@
         <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>64464.36</v>
+        <v>64458.77</v>
       </c>
       <c r="I84" t="n">
         <v>2.3</v>
@@ -6600,7 +6600,7 @@
         <v>1</v>
       </c>
       <c r="H85" t="n">
-        <v>233837.98</v>
+        <v>233815.61</v>
       </c>
       <c r="I85" t="n">
         <v>2.09</v>
@@ -6668,7 +6668,7 @@
         <v>1</v>
       </c>
       <c r="H86" t="n">
-        <v>75289.14</v>
+        <v>75282.35000000001</v>
       </c>
       <c r="I86" t="n">
         <v>2.21</v>
@@ -6736,7 +6736,7 @@
         <v>1</v>
       </c>
       <c r="H87" t="n">
-        <v>69131.12</v>
+        <v>69124.92999999999</v>
       </c>
       <c r="I87" t="n">
         <v>2.23</v>
@@ -6804,7 +6804,7 @@
         <v>1</v>
       </c>
       <c r="H88" t="n">
-        <v>47749.47</v>
+        <v>47745.08</v>
       </c>
       <c r="I88" t="n">
         <v>2.17</v>
@@ -6872,7 +6872,7 @@
         <v>1</v>
       </c>
       <c r="H89" t="n">
-        <v>55597.03</v>
+        <v>55591.84</v>
       </c>
       <c r="I89" t="n">
         <v>2.14</v>
@@ -6940,7 +6940,7 @@
         <v>1</v>
       </c>
       <c r="H90" t="n">
-        <v>129494.49</v>
+        <v>129482.91</v>
       </c>
       <c r="I90" t="n">
         <v>2.23</v>
@@ -7008,7 +7008,7 @@
         <v>1</v>
       </c>
       <c r="H91" t="n">
-        <v>90869.7</v>
+        <v>90861.52</v>
       </c>
       <c r="I91" t="n">
         <v>2.22</v>
@@ -7076,7 +7076,7 @@
         <v>1</v>
       </c>
       <c r="H92" t="n">
-        <v>103585.48</v>
+        <v>103576.1</v>
       </c>
       <c r="I92" t="n">
         <v>2.2</v>
@@ -7144,7 +7144,7 @@
         <v>1</v>
       </c>
       <c r="H93" t="n">
-        <v>55253.67</v>
+        <v>55248.88</v>
       </c>
       <c r="I93" t="n">
         <v>2.3</v>
@@ -7212,7 +7212,7 @@
         <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>205635.06</v>
+        <v>205631.26</v>
       </c>
       <c r="I94" t="n">
         <v>10.82</v>
@@ -7280,7 +7280,7 @@
         <v>1</v>
       </c>
       <c r="H95" t="n">
-        <v>173223.88</v>
+        <v>173209.1</v>
       </c>
       <c r="I95" t="n">
         <v>2.34</v>
@@ -7348,7 +7348,7 @@
         <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>105017.49</v>
+        <v>105008.31</v>
       </c>
       <c r="I96" t="n">
         <v>2.28</v>
@@ -7416,7 +7416,7 @@
         <v>1</v>
       </c>
       <c r="H97" t="n">
-        <v>78530.61</v>
+        <v>78524.02</v>
       </c>
       <c r="I97" t="n">
         <v>2.38</v>
@@ -7484,7 +7484,7 @@
         <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>231476.84</v>
+        <v>231472.64</v>
       </c>
       <c r="I98" t="n">
         <v>11.02</v>
@@ -7552,7 +7552,7 @@
         <v>1</v>
       </c>
       <c r="H99" t="n">
-        <v>69623.09</v>
+        <v>69617.3</v>
       </c>
       <c r="I99" t="n">
         <v>2.4</v>
@@ -7620,7 +7620,7 @@
         <v>1</v>
       </c>
       <c r="H100" t="n">
-        <v>60402.67</v>
+        <v>60397.67</v>
       </c>
       <c r="I100" t="n">
         <v>2.42</v>
@@ -7667,28 +7667,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Goroka Base Hospital</t>
+          <t>Goroka Provincial Hospital</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Goroka Province</t>
+          <t>Eastern Highlands</t>
         </is>
       </c>
       <c r="D101" t="n">
         <v>108000</v>
       </c>
       <c r="E101" t="n">
-        <v>378.156</v>
+        <v>378.032</v>
       </c>
       <c r="F101" t="n">
-        <v>378.156</v>
+        <v>378.032</v>
       </c>
       <c r="G101" t="n">
         <v>1</v>
       </c>
       <c r="H101" t="n">
-        <v>275553.23</v>
+        <v>275442.09</v>
       </c>
       <c r="I101" t="n">
         <v>2.55</v>
@@ -7756,7 +7756,7 @@
         <v>1</v>
       </c>
       <c r="H102" t="n">
-        <v>147087.07</v>
+        <v>147074.81</v>
       </c>
       <c r="I102" t="n">
         <v>2.37</v>
@@ -7824,7 +7824,7 @@
         <v>1</v>
       </c>
       <c r="H103" t="n">
-        <v>86972.64</v>
+        <v>86965.92</v>
       </c>
       <c r="I103" t="n">
         <v>2.56</v>
@@ -7892,7 +7892,7 @@
         <v>1</v>
       </c>
       <c r="H104" t="n">
-        <v>83990.84</v>
+        <v>83984.71000000001</v>
       </c>
       <c r="I104" t="n">
         <v>2.71</v>
@@ -7960,7 +7960,7 @@
         <v>1</v>
       </c>
       <c r="H105" t="n">
-        <v>71913.75</v>
+        <v>71908.21000000001</v>
       </c>
       <c r="I105" t="n">
         <v>2.57</v>
@@ -8028,7 +8028,7 @@
         <v>1</v>
       </c>
       <c r="H106" t="n">
-        <v>149456.19</v>
+        <v>149453.62</v>
       </c>
       <c r="I106" t="n">
         <v>11.5</v>
@@ -8096,7 +8096,7 @@
         <v>1</v>
       </c>
       <c r="H107" t="n">
-        <v>126462.93</v>
+        <v>126460.76</v>
       </c>
       <c r="I107" t="n">
         <v>11.5</v>
@@ -8164,7 +8164,7 @@
         <v>1</v>
       </c>
       <c r="H108" t="n">
-        <v>111141.19</v>
+        <v>111134.47</v>
       </c>
       <c r="I108" t="n">
         <v>3.27</v>
@@ -8232,7 +8232,7 @@
         <v>1</v>
       </c>
       <c r="H109" t="n">
-        <v>29419.73</v>
+        <v>29417.95</v>
       </c>
       <c r="I109" t="n">
         <v>3.27</v>
@@ -8300,7 +8300,7 @@
         <v>1</v>
       </c>
       <c r="H110" t="n">
-        <v>21247.58</v>
+        <v>21246.3</v>
       </c>
       <c r="I110" t="n">
         <v>3.27</v>
@@ -8368,7 +8368,7 @@
         <v>1</v>
       </c>
       <c r="H111" t="n">
-        <v>17978.72</v>
+        <v>17977.63</v>
       </c>
       <c r="I111" t="n">
         <v>3.27</v>
@@ -8436,7 +8436,7 @@
         <v>1</v>
       </c>
       <c r="H112" t="n">
-        <v>16344.29</v>
+        <v>16343.3</v>
       </c>
       <c r="I112" t="n">
         <v>3.27</v>
@@ -8488,7 +8488,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Kavieng Province</t>
+          <t>New Ireland</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -8504,7 +8504,7 @@
         <v>1</v>
       </c>
       <c r="H113" t="n">
-        <v>156686.61</v>
+        <v>156675.14</v>
       </c>
       <c r="I113" t="n">
         <v>2.7</v>
@@ -8572,7 +8572,7 @@
         <v>1</v>
       </c>
       <c r="H114" t="n">
-        <v>124268.69</v>
+        <v>124259.59</v>
       </c>
       <c r="I114" t="n">
         <v>2.7</v>
@@ -8640,7 +8640,7 @@
         <v>1</v>
       </c>
       <c r="H115" t="n">
-        <v>53159.15</v>
+        <v>53155.39</v>
       </c>
       <c r="I115" t="n">
         <v>2.8</v>
@@ -8708,7 +8708,7 @@
         <v>1</v>
       </c>
       <c r="H116" t="n">
-        <v>45925.38</v>
+        <v>45922.02</v>
       </c>
       <c r="I116" t="n">
         <v>2.7</v>
@@ -8776,7 +8776,7 @@
         <v>1</v>
       </c>
       <c r="H117" t="n">
-        <v>22382.8</v>
+        <v>22381.22</v>
       </c>
       <c r="I117" t="n">
         <v>2.8</v>
@@ -8844,7 +8844,7 @@
         <v>1</v>
       </c>
       <c r="H118" t="n">
-        <v>39169.9</v>
+        <v>39167.13</v>
       </c>
       <c r="I118" t="n">
         <v>2.8</v>
@@ -8912,7 +8912,7 @@
         <v>1</v>
       </c>
       <c r="H119" t="n">
-        <v>206339.22</v>
+        <v>206321.03</v>
       </c>
       <c r="I119" t="n">
         <v>2.24</v>
@@ -8980,7 +8980,7 @@
         <v>1</v>
       </c>
       <c r="H120" t="n">
-        <v>133007.64</v>
+        <v>132995.58</v>
       </c>
       <c r="I120" t="n">
         <v>2.18</v>
@@ -9048,7 +9048,7 @@
         <v>1</v>
       </c>
       <c r="H121" t="n">
-        <v>85579.82000000001</v>
+        <v>85572.31</v>
       </c>
       <c r="I121" t="n">
         <v>2.25</v>
@@ -9116,7 +9116,7 @@
         <v>1</v>
       </c>
       <c r="H122" t="n">
-        <v>46650.02</v>
+        <v>46645.86</v>
       </c>
       <c r="I122" t="n">
         <v>2.22</v>
@@ -9184,7 +9184,7 @@
         <v>1</v>
       </c>
       <c r="H123" t="n">
-        <v>65179.44</v>
+        <v>65174.9</v>
       </c>
       <c r="I123" t="n">
         <v>2.83</v>
@@ -9252,7 +9252,7 @@
         <v>1</v>
       </c>
       <c r="H124" t="n">
-        <v>51010</v>
+        <v>51006.44</v>
       </c>
       <c r="I124" t="n">
         <v>2.83</v>
@@ -9320,7 +9320,7 @@
         <v>1</v>
       </c>
       <c r="H125" t="n">
-        <v>202304.96</v>
+        <v>202289.54</v>
       </c>
       <c r="I125" t="n">
         <v>2.59</v>
@@ -9388,7 +9388,7 @@
         <v>1</v>
       </c>
       <c r="H126" t="n">
-        <v>82996.91</v>
+        <v>82990.58</v>
       </c>
       <c r="I126" t="n">
         <v>2.59</v>
@@ -9456,7 +9456,7 @@
         <v>1</v>
       </c>
       <c r="H127" t="n">
-        <v>42751.41</v>
+        <v>42748.25</v>
       </c>
       <c r="I127" t="n">
         <v>2.67</v>
@@ -9524,7 +9524,7 @@
         <v>1</v>
       </c>
       <c r="H128" t="n">
-        <v>106339.79</v>
+        <v>106331.68</v>
       </c>
       <c r="I128" t="n">
         <v>2.59</v>
@@ -9592,7 +9592,7 @@
         <v>1</v>
       </c>
       <c r="H129" t="n">
-        <v>64127.12</v>
+        <v>64122.37</v>
       </c>
       <c r="I129" t="n">
         <v>2.67</v>
@@ -9660,7 +9660,7 @@
         <v>1</v>
       </c>
       <c r="H130" t="n">
-        <v>187053.16</v>
+        <v>187039.78</v>
       </c>
       <c r="I130" t="n">
         <v>2.79</v>
@@ -9728,7 +9728,7 @@
         <v>1</v>
       </c>
       <c r="H131" t="n">
-        <v>146041.02</v>
+        <v>146030.64</v>
       </c>
       <c r="I131" t="n">
         <v>2.81</v>
@@ -9796,7 +9796,7 @@
         <v>1</v>
       </c>
       <c r="H132" t="n">
-        <v>123622.95</v>
+        <v>123614.25</v>
       </c>
       <c r="I132" t="n">
         <v>2.81</v>
@@ -9864,7 +9864,7 @@
         <v>1</v>
       </c>
       <c r="H133" t="n">
-        <v>50253.09</v>
+        <v>50249.49</v>
       </c>
       <c r="I133" t="n">
         <v>2.79</v>
@@ -9932,7 +9932,7 @@
         <v>1</v>
       </c>
       <c r="H134" t="n">
-        <v>19667.29</v>
+        <v>19665.9</v>
       </c>
       <c r="I134" t="n">
         <v>2.81</v>
@@ -10000,7 +10000,7 @@
         <v>1</v>
       </c>
       <c r="H135" t="n">
-        <v>44669.41</v>
+        <v>44666.22</v>
       </c>
       <c r="I135" t="n">
         <v>2.79</v>
@@ -10179,7 +10179,7 @@
         <v>2721.52</v>
       </c>
       <c r="I2" t="n">
-        <v>114313.66</v>
+        <v>114313.64</v>
       </c>
       <c r="J2" t="n">
         <v>100.39</v>
@@ -10231,7 +10231,7 @@
         <v>195.25</v>
       </c>
       <c r="I3" t="n">
-        <v>14351.99</v>
+        <v>14351.95</v>
       </c>
       <c r="J3" t="n">
         <v>322.81</v>
@@ -10289,7 +10289,7 @@
         <v>195.25</v>
       </c>
       <c r="I4" t="n">
-        <v>21869.71</v>
+        <v>21869.64</v>
       </c>
       <c r="J4" t="n">
         <v>483.47</v>
@@ -10347,7 +10347,7 @@
         <v>195.25</v>
       </c>
       <c r="I5" t="n">
-        <v>12301.71</v>
+        <v>12301.67</v>
       </c>
       <c r="J5" t="n">
         <v>416.21</v>
@@ -10405,7 +10405,7 @@
         <v>2892.77</v>
       </c>
       <c r="I6" t="n">
-        <v>111381.21</v>
+        <v>111381.19</v>
       </c>
       <c r="J6" t="n">
         <v>255.89</v>
@@ -10457,7 +10457,7 @@
         <v>216.81</v>
       </c>
       <c r="I7" t="n">
-        <v>33390.95</v>
+        <v>33390.86</v>
       </c>
       <c r="J7" t="n">
         <v>538.08</v>
@@ -10515,7 +10515,7 @@
         <v>200.68</v>
       </c>
       <c r="I8" t="n">
-        <v>27395.49</v>
+        <v>27395.41</v>
       </c>
       <c r="J8" t="n">
         <v>1162.1</v>
@@ -10573,7 +10573,7 @@
         <v>200.68</v>
       </c>
       <c r="I9" t="n">
-        <v>19668.56</v>
+        <v>19668.5</v>
       </c>
       <c r="J9" t="n">
         <v>1251.46</v>
@@ -10631,7 +10631,7 @@
         <v>200.68</v>
       </c>
       <c r="I10" t="n">
-        <v>21775.9</v>
+        <v>21775.84</v>
       </c>
       <c r="J10" t="n">
         <v>767.52</v>
@@ -10689,7 +10689,7 @@
         <v>200.68</v>
       </c>
       <c r="I11" t="n">
-        <v>5268.36</v>
+        <v>5268.35</v>
       </c>
       <c r="J11" t="n">
         <v>955.4400000000001</v>
@@ -10747,7 +10747,7 @@
         <v>2776.94</v>
       </c>
       <c r="I12" t="n">
-        <v>87481.02</v>
+        <v>87481</v>
       </c>
       <c r="J12" t="n">
         <v>617.75</v>
@@ -10799,7 +10799,7 @@
         <v>2776.94</v>
       </c>
       <c r="I13" t="n">
-        <v>82620.96000000001</v>
+        <v>82620.95</v>
       </c>
       <c r="J13" t="n">
         <v>684.9400000000001</v>
@@ -10851,7 +10851,7 @@
         <v>186.08</v>
       </c>
       <c r="I14" t="n">
-        <v>40383.81</v>
+        <v>40383.69</v>
       </c>
       <c r="J14" t="n">
         <v>448.61</v>
@@ -10909,7 +10909,7 @@
         <v>186.08</v>
       </c>
       <c r="I15" t="n">
-        <v>11072.98</v>
+        <v>11072.95</v>
       </c>
       <c r="J15" t="n">
         <v>358.09</v>
@@ -10967,7 +10967,7 @@
         <v>243.77</v>
       </c>
       <c r="I16" t="n">
-        <v>60582.07</v>
+        <v>60581.93</v>
       </c>
       <c r="J16" t="n">
         <v>323.36</v>
@@ -11025,7 +11025,7 @@
         <v>243.77</v>
       </c>
       <c r="I17" t="n">
-        <v>18771.91</v>
+        <v>18771.86</v>
       </c>
       <c r="J17" t="n">
         <v>308.79</v>
@@ -11083,7 +11083,7 @@
         <v>243.77</v>
       </c>
       <c r="I18" t="n">
-        <v>11092.49</v>
+        <v>11092.47</v>
       </c>
       <c r="J18" t="n">
         <v>447.3</v>
@@ -11141,7 +11141,7 @@
         <v>243.77</v>
       </c>
       <c r="I19" t="n">
-        <v>9385.950000000001</v>
+        <v>9385.93</v>
       </c>
       <c r="J19" t="n">
         <v>459</v>
@@ -11199,7 +11199,7 @@
         <v>243.77</v>
       </c>
       <c r="I20" t="n">
-        <v>11945.76</v>
+        <v>11945.73</v>
       </c>
       <c r="J20" t="n">
         <v>306.91</v>
@@ -11257,7 +11257,7 @@
         <v>2829.85</v>
       </c>
       <c r="I21" t="n">
-        <v>99053.39999999999</v>
+        <v>99053.38</v>
       </c>
       <c r="J21" t="n">
         <v>315.98</v>
@@ -11309,7 +11309,7 @@
         <v>229.39</v>
       </c>
       <c r="I22" t="n">
-        <v>33722.74</v>
+        <v>33722.65</v>
       </c>
       <c r="J22" t="n">
         <v>117.11</v>
@@ -11367,7 +11367,7 @@
         <v>229.39</v>
       </c>
       <c r="I23" t="n">
-        <v>13649.68</v>
+        <v>13649.65</v>
       </c>
       <c r="J23" t="n">
         <v>106.12</v>
@@ -11425,7 +11425,7 @@
         <v>2715.69</v>
       </c>
       <c r="I24" t="n">
-        <v>180608.72</v>
+        <v>180608.68</v>
       </c>
       <c r="J24" t="n">
         <v>64.55</v>
@@ -11477,7 +11477,7 @@
         <v>322.79</v>
       </c>
       <c r="I25" t="n">
-        <v>29376.07</v>
+        <v>29376.02</v>
       </c>
       <c r="J25" t="n">
         <v>106.06</v>
@@ -11535,7 +11535,7 @@
         <v>293.91</v>
       </c>
       <c r="I26" t="n">
-        <v>22633.3</v>
+        <v>22633.26</v>
       </c>
       <c r="J26" t="n">
         <v>80.93000000000001</v>
@@ -11593,7 +11593,7 @@
         <v>2653.05</v>
       </c>
       <c r="I27" t="n">
-        <v>111437.63</v>
+        <v>111437.6</v>
       </c>
       <c r="J27" t="n">
         <v>98.78</v>
@@ -11645,7 +11645,7 @@
         <v>2918.47</v>
       </c>
       <c r="I28" t="n">
-        <v>143017.1</v>
+        <v>143017.07</v>
       </c>
       <c r="J28" t="n">
         <v>139.33</v>
@@ -11697,7 +11697,7 @@
         <v>287.67</v>
       </c>
       <c r="I29" t="n">
-        <v>47325.43</v>
+        <v>47325.34</v>
       </c>
       <c r="J29" t="n">
         <v>698.29</v>
@@ -11755,7 +11755,7 @@
         <v>3094.04</v>
       </c>
       <c r="I30" t="n">
-        <v>173281.24</v>
+        <v>173281.18</v>
       </c>
       <c r="J30" t="n">
         <v>201.21</v>
@@ -11804,10 +11804,10 @@
         <v>66.5057</v>
       </c>
       <c r="H31" t="n">
-        <v>2637.38</v>
+        <v>2637.37</v>
       </c>
       <c r="I31" t="n">
-        <v>175400.54</v>
+        <v>175400.46</v>
       </c>
       <c r="J31" t="n">
         <v>53.72</v>
@@ -11859,7 +11859,7 @@
         <v>2694.46</v>
       </c>
       <c r="I32" t="n">
-        <v>198059.74</v>
+        <v>198059.65</v>
       </c>
       <c r="J32" t="n">
         <v>94.98999999999999</v>
@@ -11911,7 +11911,7 @@
         <v>2829.85</v>
       </c>
       <c r="I33" t="n">
-        <v>128769.41</v>
+        <v>128769.39</v>
       </c>
       <c r="J33" t="n">
         <v>120.54</v>
@@ -11963,7 +11963,7 @@
         <v>2829.85</v>
       </c>
       <c r="I34" t="n">
-        <v>108958.74</v>
+        <v>108958.71</v>
       </c>
       <c r="J34" t="n">
         <v>130.5</v>
@@ -12015,7 +12015,7 @@
         <v>479.26</v>
       </c>
       <c r="I35" t="n">
-        <v>57037.32</v>
+        <v>57037.25</v>
       </c>
       <c r="J35" t="n">
         <v>477.86</v>
@@ -12073,7 +12073,7 @@
         <v>479.26</v>
       </c>
       <c r="I36" t="n">
-        <v>15098.11</v>
+        <v>15098.1</v>
       </c>
       <c r="J36" t="n">
         <v>482.12</v>
@@ -12131,7 +12131,7 @@
         <v>479.26</v>
       </c>
       <c r="I37" t="n">
-        <v>10904.19</v>
+        <v>10904.18</v>
       </c>
       <c r="J37" t="n">
         <v>480.24</v>
@@ -12189,7 +12189,7 @@
         <v>479.26</v>
       </c>
       <c r="I38" t="n">
-        <v>9226.620000000001</v>
+        <v>9226.610000000001</v>
       </c>
       <c r="J38" t="n">
         <v>481.26</v>
@@ -12247,7 +12247,7 @@
         <v>479.26</v>
       </c>
       <c r="I39" t="n">
-        <v>8387.84</v>
+        <v>8387.83</v>
       </c>
       <c r="J39" t="n">
         <v>412.79</v>
@@ -12305,7 +12305,7 @@
         <v>317.17</v>
       </c>
       <c r="I40" t="n">
-        <v>64391.76</v>
+        <v>64391.64</v>
       </c>
       <c r="J40" t="n">
         <v>311.37</v>
@@ -12363,7 +12363,7 @@
         <v>317.17</v>
       </c>
       <c r="I41" t="n">
-        <v>51069.33</v>
+        <v>51069.23</v>
       </c>
       <c r="J41" t="n">
         <v>94.95999999999999</v>
@@ -12421,7 +12421,7 @@
         <v>344.7</v>
       </c>
       <c r="I42" t="n">
-        <v>22924.63</v>
+        <v>22924.59</v>
       </c>
       <c r="J42" t="n">
         <v>182.8</v>
@@ -12479,7 +12479,7 @@
         <v>317.17</v>
       </c>
       <c r="I43" t="n">
-        <v>18873.45</v>
+        <v>18873.41</v>
       </c>
       <c r="J43" t="n">
         <v>175.95</v>
@@ -12537,7 +12537,7 @@
         <v>344.7</v>
       </c>
       <c r="I44" t="n">
-        <v>9652.469999999999</v>
+        <v>9652.459999999999</v>
       </c>
       <c r="J44" t="n">
         <v>205.12</v>
@@ -12595,7 +12595,7 @@
         <v>344.7</v>
       </c>
       <c r="I45" t="n">
-        <v>16891.83</v>
+        <v>16891.8</v>
       </c>
       <c r="J45" t="n">
         <v>368.78</v>
@@ -12653,7 +12653,7 @@
         <v>355</v>
       </c>
       <c r="I46" t="n">
-        <v>28579.76</v>
+        <v>28579.72</v>
       </c>
       <c r="J46" t="n">
         <v>240.83</v>
@@ -12711,7 +12711,7 @@
         <v>355</v>
       </c>
       <c r="I47" t="n">
-        <v>22366.77</v>
+        <v>22366.73</v>
       </c>
       <c r="J47" t="n">
         <v>189.94</v>
@@ -12769,7 +12769,7 @@
         <v>286.36</v>
       </c>
       <c r="I48" t="n">
-        <v>78184.3</v>
+        <v>78184.14999999999</v>
       </c>
       <c r="J48" t="n">
         <v>328.7</v>
@@ -12827,7 +12827,7 @@
         <v>286.36</v>
       </c>
       <c r="I49" t="n">
-        <v>32075.61</v>
+        <v>32075.55</v>
       </c>
       <c r="J49" t="n">
         <v>328.88</v>
@@ -12885,7 +12885,7 @@
         <v>308.74</v>
       </c>
       <c r="I50" t="n">
-        <v>17290.76</v>
+        <v>17290.73</v>
       </c>
       <c r="J50" t="n">
         <v>369.95</v>
@@ -12943,7 +12943,7 @@
         <v>286.36</v>
       </c>
       <c r="I51" t="n">
-        <v>41096.88</v>
+        <v>41096.8</v>
       </c>
       <c r="J51" t="n">
         <v>215.37</v>
@@ -13001,7 +13001,7 @@
         <v>308.74</v>
       </c>
       <c r="I52" t="n">
-        <v>25936.15</v>
+        <v>25936.1</v>
       </c>
       <c r="J52" t="n">
         <v>445.5</v>
@@ -13059,7 +13059,7 @@
         <v>348.06</v>
       </c>
       <c r="I53" t="n">
-        <v>53606.17</v>
+        <v>53606.08</v>
       </c>
       <c r="J53" t="n">
         <v>577.77</v>
@@ -13117,7 +13117,7 @@
         <v>348.06</v>
       </c>
       <c r="I54" t="n">
-        <v>8528.25</v>
+        <v>8528.24</v>
       </c>
       <c r="J54" t="n">
         <v>267.72</v>
@@ -13169,13 +13169,13 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>587.5544</v>
+        <v>588.0504</v>
       </c>
       <c r="H55" t="n">
         <v>55.64</v>
       </c>
       <c r="I55" t="n">
-        <v>32691.99</v>
+        <v>32716.97</v>
       </c>
       <c r="J55" t="n">
         <v>4.28</v>
@@ -13224,10 +13224,10 @@
         <v>462.0396</v>
       </c>
       <c r="H56" t="n">
-        <v>60.04</v>
+        <v>60.03</v>
       </c>
       <c r="I56" t="n">
-        <v>27738.74</v>
+        <v>27738.47</v>
       </c>
       <c r="J56" t="n">
         <v>13.54</v>
@@ -13279,7 +13279,7 @@
         <v>54.32</v>
       </c>
       <c r="I57" t="n">
-        <v>11598.56</v>
+        <v>11598.44</v>
       </c>
       <c r="J57" t="n">
         <v>1.51</v>
@@ -13331,7 +13331,7 @@
         <v>56.12</v>
       </c>
       <c r="I58" t="n">
-        <v>10606.96</v>
+        <v>10606.85</v>
       </c>
       <c r="J58" t="n">
         <v>5.29</v>
@@ -13383,7 +13383,7 @@
         <v>58.93</v>
       </c>
       <c r="I59" t="n">
-        <v>7838.18</v>
+        <v>7838.11</v>
       </c>
       <c r="J59" t="n">
         <v>11.21</v>
@@ -13435,7 +13435,7 @@
         <v>110.15</v>
       </c>
       <c r="I60" t="n">
-        <v>18120.56</v>
+        <v>18120.47</v>
       </c>
       <c r="J60" t="n">
         <v>103.3</v>
@@ -13487,7 +13487,7 @@
         <v>171.81</v>
       </c>
       <c r="I61" t="n">
-        <v>25258.54</v>
+        <v>25258.46</v>
       </c>
       <c r="J61" t="n">
         <v>171.76</v>
@@ -13539,7 +13539,7 @@
         <v>187.28</v>
       </c>
       <c r="I62" t="n">
-        <v>12455.07</v>
+        <v>12455.04</v>
       </c>
       <c r="J62" t="n">
         <v>218.82</v>
@@ -13591,7 +13591,7 @@
         <v>152.79</v>
       </c>
       <c r="I63" t="n">
-        <v>20322.3</v>
+        <v>20322.22</v>
       </c>
       <c r="J63" t="n">
         <v>183.69</v>
@@ -13643,7 +13643,7 @@
         <v>141.81</v>
       </c>
       <c r="I64" t="n">
-        <v>7941.95</v>
+        <v>7941.92</v>
       </c>
       <c r="J64" t="n">
         <v>125.96</v>
@@ -13695,7 +13695,7 @@
         <v>231.01</v>
       </c>
       <c r="I65" t="n">
-        <v>46899.45</v>
+        <v>46899.34</v>
       </c>
       <c r="J65" t="n">
         <v>331.17</v>
@@ -13747,7 +13747,7 @@
         <v>240.29</v>
       </c>
       <c r="I66" t="n">
-        <v>20186.1</v>
+        <v>20186.05</v>
       </c>
       <c r="J66" t="n">
         <v>276.29</v>
@@ -13793,13 +13793,13 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>656.3203999999999</v>
+        <v>658.0564000000001</v>
       </c>
       <c r="H67" t="n">
-        <v>105.37</v>
+        <v>105.36</v>
       </c>
       <c r="I67" t="n">
-        <v>69156.57000000001</v>
+        <v>69331.11</v>
       </c>
       <c r="J67" t="n">
         <v>1.06</v>
@@ -13851,7 +13851,7 @@
         <v>162.73</v>
       </c>
       <c r="I68" t="n">
-        <v>30758.9</v>
+        <v>30758.79</v>
       </c>
       <c r="J68" t="n">
         <v>113.39</v>
@@ -13903,7 +13903,7 @@
         <v>185.55</v>
       </c>
       <c r="I69" t="n">
-        <v>20134.38</v>
+        <v>20134.32</v>
       </c>
       <c r="J69" t="n">
         <v>129.6</v>
@@ -13955,7 +13955,7 @@
         <v>232.99</v>
       </c>
       <c r="I70" t="n">
-        <v>29359.15</v>
+        <v>29359.08</v>
       </c>
       <c r="J70" t="n">
         <v>209.49</v>
@@ -14007,7 +14007,7 @@
         <v>156.71</v>
       </c>
       <c r="I71" t="n">
-        <v>12616.57</v>
+        <v>12616.52</v>
       </c>
       <c r="J71" t="n">
         <v>101.42</v>
@@ -14059,7 +14059,7 @@
         <v>137.04</v>
       </c>
       <c r="I72" t="n">
-        <v>46050.4</v>
+        <v>46050.21</v>
       </c>
       <c r="J72" t="n">
         <v>1.39</v>
@@ -14111,7 +14111,7 @@
         <v>274.92</v>
       </c>
       <c r="I73" t="n">
-        <v>39454.23</v>
+        <v>39454.15</v>
       </c>
       <c r="J73" t="n">
         <v>202.79</v>
@@ -14163,7 +14163,7 @@
         <v>228.9</v>
       </c>
       <c r="I74" t="n">
-        <v>22434.55</v>
+        <v>22434.49</v>
       </c>
       <c r="J74" t="n">
         <v>132.55</v>
@@ -14215,7 +14215,7 @@
         <v>203.25</v>
       </c>
       <c r="I75" t="n">
-        <v>51222.52</v>
+        <v>51222.24</v>
       </c>
       <c r="J75" t="n">
         <v>122.66</v>
@@ -14267,7 +14267,7 @@
         <v>182.26</v>
       </c>
       <c r="I76" t="n">
-        <v>30622.9</v>
+        <v>30622.71</v>
       </c>
       <c r="J76" t="n">
         <v>80.92</v>
@@ -14319,7 +14319,7 @@
         <v>243.18</v>
       </c>
       <c r="I77" t="n">
-        <v>32346</v>
+        <v>32345.85</v>
       </c>
       <c r="J77" t="n">
         <v>166.27</v>
@@ -14371,7 +14371,7 @@
         <v>279.19</v>
       </c>
       <c r="I78" t="n">
-        <v>40066.79</v>
+        <v>40066.63</v>
       </c>
       <c r="J78" t="n">
         <v>226.91</v>
@@ -14423,7 +14423,7 @@
         <v>212.62</v>
       </c>
       <c r="I79" t="n">
-        <v>21582.97</v>
+        <v>21582.85</v>
       </c>
       <c r="J79" t="n">
         <v>114.8</v>
@@ -14475,7 +14475,7 @@
         <v>227.61</v>
       </c>
       <c r="I80" t="n">
-        <v>25494.96</v>
+        <v>25494.83</v>
       </c>
       <c r="J80" t="n">
         <v>140.05</v>
@@ -14527,7 +14527,7 @@
         <v>292.73</v>
       </c>
       <c r="I81" t="n">
-        <v>86070.17999999999</v>
+        <v>86069.84</v>
       </c>
       <c r="J81" t="n">
         <v>249.72</v>
@@ -14579,7 +14579,7 @@
         <v>318.72</v>
       </c>
       <c r="I82" t="n">
-        <v>47972.22</v>
+        <v>47972.05</v>
       </c>
       <c r="J82" t="n">
         <v>293.5</v>
@@ -14631,7 +14631,7 @@
         <v>305.59</v>
       </c>
       <c r="I83" t="n">
-        <v>33159.49</v>
+        <v>33159.37</v>
       </c>
       <c r="J83" t="n">
         <v>271.38</v>
@@ -14683,7 +14683,7 @@
         <v>264.97</v>
       </c>
       <c r="I84" t="n">
-        <v>25041.51</v>
+        <v>25041.41</v>
       </c>
       <c r="J84" t="n">
         <v>202.96</v>
@@ -14735,7 +14735,7 @@
         <v>205.33</v>
       </c>
       <c r="I85" t="n">
-        <v>56778</v>
+        <v>56777.68</v>
       </c>
       <c r="J85" t="n">
         <v>126.8</v>
@@ -14787,7 +14787,7 @@
         <v>190.78</v>
       </c>
       <c r="I86" t="n">
-        <v>29382.55</v>
+        <v>29382.37</v>
       </c>
       <c r="J86" t="n">
         <v>97.86</v>
@@ -14839,7 +14839,7 @@
         <v>220.64</v>
       </c>
       <c r="I87" t="n">
-        <v>27803.45</v>
+        <v>27803.31</v>
       </c>
       <c r="J87" t="n">
         <v>128.31</v>
@@ -14891,7 +14891,7 @@
         <v>244.11</v>
       </c>
       <c r="I88" t="n">
-        <v>33324.47</v>
+        <v>33324.31</v>
       </c>
       <c r="J88" t="n">
         <v>167.84</v>
@@ -14943,7 +14943,7 @@
         <v>239.51</v>
       </c>
       <c r="I89" t="n">
-        <v>19281.95</v>
+        <v>19281.86</v>
       </c>
       <c r="J89" t="n">
         <v>160.08</v>
@@ -14995,7 +14995,7 @@
         <v>203.13</v>
       </c>
       <c r="I90" t="n">
-        <v>19908.23</v>
+        <v>19908.12</v>
       </c>
       <c r="J90" t="n">
         <v>98.81</v>
@@ -15047,7 +15047,7 @@
         <v>141.86</v>
       </c>
       <c r="I91" t="n">
-        <v>55613.44</v>
+        <v>55613</v>
       </c>
       <c r="J91" t="n">
         <v>2.42</v>
@@ -15099,7 +15099,7 @@
         <v>178.01</v>
       </c>
       <c r="I92" t="n">
-        <v>21185.26</v>
+        <v>21185.13</v>
       </c>
       <c r="J92" t="n">
         <v>56.51</v>
@@ -15151,7 +15151,7 @@
         <v>182.48</v>
       </c>
       <c r="I93" t="n">
-        <v>19801.11</v>
+        <v>19800.99</v>
       </c>
       <c r="J93" t="n">
         <v>64.04000000000001</v>
@@ -15203,7 +15203,7 @@
         <v>165.45</v>
       </c>
       <c r="I94" t="n">
-        <v>12741.08</v>
+        <v>12740.99</v>
       </c>
       <c r="J94" t="n">
         <v>35.36</v>
@@ -15255,7 +15255,7 @@
         <v>156.29</v>
       </c>
       <c r="I95" t="n">
-        <v>14223.48</v>
+        <v>14223.38</v>
       </c>
       <c r="J95" t="n">
         <v>29.25</v>
@@ -15307,7 +15307,7 @@
         <v>183.23</v>
       </c>
       <c r="I96" t="n">
-        <v>37199.64</v>
+        <v>37199.41</v>
       </c>
       <c r="J96" t="n">
         <v>82.84999999999999</v>
@@ -15359,7 +15359,7 @@
         <v>178.57</v>
       </c>
       <c r="I97" t="n">
-        <v>25626.79</v>
+        <v>25626.63</v>
       </c>
       <c r="J97" t="n">
         <v>73.56999999999999</v>
@@ -15411,7 +15411,7 @@
         <v>175.03</v>
       </c>
       <c r="I98" t="n">
-        <v>28794.83</v>
+        <v>28794.64</v>
       </c>
       <c r="J98" t="n">
         <v>66.53</v>
@@ -15463,7 +15463,7 @@
         <v>203.11</v>
       </c>
       <c r="I99" t="n">
-        <v>17062.7</v>
+        <v>17062.61</v>
       </c>
       <c r="J99" t="n">
         <v>98.78</v>
@@ -15512,10 +15512,10 @@
         <v>259.0222</v>
       </c>
       <c r="H100" t="n">
-        <v>214.15</v>
+        <v>214.14</v>
       </c>
       <c r="I100" t="n">
-        <v>55468.38</v>
+        <v>55468.09</v>
       </c>
       <c r="J100" t="n">
         <v>144.34</v>
@@ -15567,7 +15567,7 @@
         <v>197.61</v>
       </c>
       <c r="I101" t="n">
-        <v>31818.13</v>
+        <v>31817.95</v>
       </c>
       <c r="J101" t="n">
         <v>111.45</v>
@@ -15619,7 +15619,7 @@
         <v>225.24</v>
       </c>
       <c r="I102" t="n">
-        <v>26018.03</v>
+        <v>26017.89</v>
       </c>
       <c r="J102" t="n">
         <v>136.06</v>
@@ -15671,7 +15671,7 @@
         <v>231.27</v>
       </c>
       <c r="I103" t="n">
-        <v>23475.67</v>
+        <v>23475.55</v>
       </c>
       <c r="J103" t="n">
         <v>178.4</v>
@@ -15723,7 +15723,7 @@
         <v>235.64</v>
       </c>
       <c r="I104" t="n">
-        <v>20620.4</v>
+        <v>20620.3</v>
       </c>
       <c r="J104" t="n">
         <v>153.57</v>
@@ -15769,13 +15769,13 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>378.1564</v>
+        <v>378.0324</v>
       </c>
       <c r="H105" t="n">
         <v>274.06</v>
       </c>
       <c r="I105" t="n">
-        <v>103637.48</v>
+        <v>103603.85</v>
       </c>
       <c r="J105" t="n">
         <v>334.85</v>
@@ -15827,7 +15827,7 @@
         <v>223.15</v>
       </c>
       <c r="I106" t="n">
-        <v>48427.06</v>
+        <v>48426.94</v>
       </c>
       <c r="J106" t="n">
         <v>233.57</v>
@@ -15879,7 +15879,7 @@
         <v>276.18</v>
       </c>
       <c r="I107" t="n">
-        <v>32868.77</v>
+        <v>32868.7</v>
       </c>
       <c r="J107" t="n">
         <v>282.24</v>
@@ -15931,7 +15931,7 @@
         <v>319.43</v>
       </c>
       <c r="I108" t="n">
-        <v>34660.83</v>
+        <v>34660.77</v>
       </c>
       <c r="J108" t="n">
         <v>355.07</v>
@@ -15980,10 +15980,10 @@
         <v>98.00839999999999</v>
       </c>
       <c r="H109" t="n">
-        <v>279.14</v>
+        <v>279.13</v>
       </c>
       <c r="I109" t="n">
-        <v>27357.61</v>
+        <v>27357.56</v>
       </c>
       <c r="J109" t="n">
         <v>287.21</v>
@@ -16035,7 +16035,7 @@
         <v>186.13</v>
       </c>
       <c r="I110" t="n">
-        <v>59940.49</v>
+        <v>59940.31</v>
       </c>
       <c r="J110" t="n">
         <v>31.5</v>
@@ -16087,7 +16087,7 @@
         <v>168.32</v>
       </c>
       <c r="I111" t="n">
-        <v>35938.92</v>
+        <v>35938.8</v>
       </c>
       <c r="J111" t="n">
         <v>1.35</v>
@@ -16139,7 +16139,7 @@
         <v>188.79</v>
       </c>
       <c r="I112" t="n">
-        <v>25110.79</v>
+        <v>25110.71</v>
       </c>
       <c r="J112" t="n">
         <v>36.5</v>
@@ -16191,7 +16191,7 @@
         <v>180.02</v>
       </c>
       <c r="I113" t="n">
-        <v>13232.92</v>
+        <v>13232.87</v>
       </c>
       <c r="J113" t="n">
         <v>19.98</v>
@@ -16243,7 +16243,7 @@
         <v>259.81</v>
       </c>
       <c r="I114" t="n">
-        <v>80027.37</v>
+        <v>80027.03</v>
       </c>
       <c r="J114" t="n">
         <v>1.35</v>
@@ -16301,7 +16301,7 @@
         <v>259.81</v>
       </c>
       <c r="I115" t="n">
-        <v>47288.9</v>
+        <v>47288.7</v>
       </c>
       <c r="J115" t="n">
         <v>83.08</v>
@@ -16359,7 +16359,7 @@
         <v>270.32</v>
       </c>
       <c r="I116" t="n">
-        <v>41632.44</v>
+        <v>41632.27</v>
       </c>
       <c r="J116" t="n">
         <v>87.33</v>
@@ -16417,7 +16417,7 @@
         <v>343.94</v>
       </c>
       <c r="I117" t="n">
-        <v>28893.78</v>
+        <v>28893.68</v>
       </c>
       <c r="J117" t="n">
         <v>180.52</v>
@@ -16475,7 +16475,7 @@
         <v>259.81</v>
       </c>
       <c r="I118" t="n">
-        <v>30010.27</v>
+        <v>30010.13</v>
       </c>
       <c r="J118" t="n">
         <v>51.66</v>
@@ -16533,7 +16533,7 @@
         <v>259.81</v>
       </c>
       <c r="I119" t="n">
-        <v>24553.85</v>
+        <v>24553.75</v>
       </c>
       <c r="J119" t="n">
         <v>88.25</v>
@@ -16591,7 +16591,7 @@
         <v>323.79</v>
       </c>
       <c r="I120" t="n">
-        <v>17000.64</v>
+        <v>17000.58</v>
       </c>
       <c r="J120" t="n">
         <v>108.43</v>
@@ -16649,7 +16649,7 @@
         <v>267.66</v>
       </c>
       <c r="I121" t="n">
-        <v>36538.72</v>
+        <v>36538.56</v>
       </c>
       <c r="J121" t="n">
         <v>186.92</v>
@@ -16707,7 +16707,7 @@
         <v>275.17</v>
       </c>
       <c r="I122" t="n">
-        <v>23116.05</v>
+        <v>23115.95</v>
       </c>
       <c r="J122" t="n">
         <v>220.55</v>
@@ -16765,7 +16765,7 @@
         <v>265.49</v>
       </c>
       <c r="I123" t="n">
-        <v>20444.57</v>
+        <v>20444.48</v>
       </c>
       <c r="J123" t="n">
         <v>159.88</v>
@@ -16823,7 +16823,7 @@
         <v>2265.82</v>
       </c>
       <c r="I124" t="n">
-        <v>142758.84</v>
+        <v>142758.77</v>
       </c>
       <c r="J124" t="n">
         <v>283.17</v>
@@ -16875,7 +16875,7 @@
         <v>1757.36</v>
       </c>
       <c r="I125" t="n">
-        <v>79966.8</v>
+        <v>79966.75</v>
       </c>
       <c r="J125" t="n">
         <v>271.16</v>
@@ -16927,7 +16927,7 @@
         <v>2291.31</v>
       </c>
       <c r="I126" t="n">
-        <v>88223.09</v>
+        <v>88223.05</v>
       </c>
       <c r="J126" t="n">
         <v>244.81</v>
@@ -16979,7 +16979,7 @@
         <v>493.41</v>
       </c>
       <c r="I127" t="n">
-        <v>50085.91</v>
+        <v>50085.86</v>
       </c>
       <c r="J127" t="n">
         <v>259.4</v>
@@ -17037,7 +17037,7 @@
         <v>437.68</v>
       </c>
       <c r="I128" t="n">
-        <v>32172.29</v>
+        <v>32172.25</v>
       </c>
       <c r="J128" t="n">
         <v>310.17</v>
@@ -17095,7 +17095,7 @@
         <v>374.9</v>
       </c>
       <c r="I129" t="n">
-        <v>31494.61</v>
+        <v>31494.57</v>
       </c>
       <c r="J129" t="n">
         <v>72.75</v>
@@ -17153,7 +17153,7 @@
         <v>374.9</v>
       </c>
       <c r="I130" t="n">
-        <v>18371.86</v>
+        <v>18371.83</v>
       </c>
       <c r="J130" t="n">
         <v>49.73</v>
@@ -17211,7 +17211,7 @@
         <v>408.35</v>
       </c>
       <c r="I131" t="n">
-        <v>21440.41</v>
+        <v>21440.38</v>
       </c>
       <c r="J131" t="n">
         <v>133.75</v>
@@ -17269,7 +17269,7 @@
         <v>342.98</v>
       </c>
       <c r="I132" t="n">
-        <v>80436.69</v>
+        <v>80436.42999999999</v>
       </c>
       <c r="J132" t="n">
         <v>0.48</v>
@@ -17327,7 +17327,7 @@
         <v>347.74</v>
       </c>
       <c r="I133" t="n">
-        <v>63293.92</v>
+        <v>63293.71</v>
       </c>
       <c r="J133" t="n">
         <v>161.8</v>
@@ -17385,7 +17385,7 @@
         <v>342.98</v>
       </c>
       <c r="I134" t="n">
-        <v>21609.86</v>
+        <v>21609.79</v>
       </c>
       <c r="J134" t="n">
         <v>93.33</v>
@@ -17443,7 +17443,7 @@
         <v>342.98</v>
       </c>
       <c r="I135" t="n">
-        <v>19208.76</v>
+        <v>19208.7</v>
       </c>
       <c r="J135" t="n">
         <v>18.09</v>
@@ -17563,19 +17563,19 @@
         <v>1034000</v>
       </c>
       <c r="D5" t="n">
-        <v>3617.1</v>
+        <v>3619.3</v>
       </c>
       <c r="E5" t="n">
-        <v>3617.1</v>
+        <v>3619.3</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>2052014.24</v>
+        <v>2053024.72</v>
       </c>
       <c r="H5" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="I5" t="n">
         <v>0.0537</v>
@@ -17603,7 +17603,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>2145848.77</v>
+        <v>2145664.51</v>
       </c>
       <c r="H6" t="n">
         <v>2.32</v>
@@ -17634,7 +17634,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>2326389.41</v>
+        <v>2326191.27</v>
       </c>
       <c r="H7" t="n">
         <v>2.34</v>
@@ -17656,16 +17656,16 @@
         <v>967500</v>
       </c>
       <c r="D8" t="n">
-        <v>3386.7</v>
+        <v>3386.5</v>
       </c>
       <c r="E8" t="n">
-        <v>3386.7</v>
+        <v>3386.5</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>2480006.39</v>
+        <v>2479724.45</v>
       </c>
       <c r="H8" t="n">
         <v>2.56</v>
@@ -17696,7 +17696,7 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>4419286.44</v>
+        <v>4419093.61</v>
       </c>
       <c r="H9" t="n">
         <v>4.54</v>
@@ -17741,7 +17741,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>One-off cost 4,509,900 PGK · annual change -1,845,604 PGK · payback 2.44 years</t>
+          <t>One-off cost 4,509,900 PGK · annual change 2,179,520 PGK · payback n/a years</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-6.xlsx
+++ b/docs/app/api/files/results-6.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 18:35 UTC · 43 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 19:24 UTC · 47 ms</t>
         </is>
       </c>
     </row>
@@ -798,6 +798,157 @@
       <c r="E16" t="inlineStr">
         <is>
           <t>flat</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Share of demand volume that is estimated</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Facilities with estimated demand</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>134</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Total annual cost with estimates 30% lower</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>11733588.99</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Fill rate (volume) with estimates 30% lower</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Fill rate, most vulnerable quintile with estimates 30% lower</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Hubs open with estimates 30% lower</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>8</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Total annual cost with estimates 30% higher</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>15099728.18</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fill rate (volume) with estimates 30% higher</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.9982</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Fill rate, most vulnerable quintile with estimates 30% higher</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Hubs open with estimates 30% higher</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>8</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>count</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-6.xlsx
+++ b/docs/app/api/files/results-6.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 19:24 UTC · 47 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 19:51 UTC · 148 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-6.xlsx
+++ b/docs/app/api/files/results-6.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 19:51 UTC · 148 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:36 UTC · 98 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-6.xlsx
+++ b/docs/app/api/files/results-6.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:36 UTC · 98 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:48 UTC · 121 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-6.xlsx
+++ b/docs/app/api/files/results-6.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:48 UTC · 121 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:58 UTC · 109 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-6.xlsx
+++ b/docs/app/api/files/results-6.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:58 UTC · 109 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:08 UTC · 195 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-6.xlsx
+++ b/docs/app/api/files/results-6.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:08 UTC · 195 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:19 UTC · 176 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-6.xlsx
+++ b/docs/app/api/files/results-6.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:19 UTC · 176 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:28 UTC · 158 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-6.xlsx
+++ b/docs/app/api/files/results-6.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:28 UTC · 158 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:40 UTC · 153 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-6.xlsx
+++ b/docs/app/api/files/results-6.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:40 UTC · 153 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-30 15:56 UTC · 107 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-6.xlsx
+++ b/docs/app/api/files/results-6.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-30 15:56 UTC · 107 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-10-06 14:14 UTC · 54 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-6.xlsx
+++ b/docs/app/api/files/results-6.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-10-06 14:14 UTC · 54 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-10-06 15:06 UTC · 43 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-6.xlsx
+++ b/docs/app/api/files/results-6.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-10-06 15:06 UTC · 43 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-10-06 15:14 UTC · 44 ms</t>
         </is>
       </c>
     </row>
